--- a/resources/library/xlsx/noriva-restaurant-feasibility-study-template.xlsx
+++ b/resources/library/xlsx/noriva-restaurant-feasibility-study-template.xlsx
@@ -2,29 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Go No-Go Summary" sheetId="1" r:id="R29cff43b7ec64a08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="Rabc50ddbe6e64729"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Overview" sheetId="3" r:id="Re3369bb1f917437e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Concept" sheetId="4" r:id="R2aedf975de4f4fcf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market Assumptions" sheetId="5" r:id="Ra1141b57dc374c33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Location" sheetId="6" r:id="R3ef843a9b57840b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target Customer" sheetId="7" r:id="R810b837d59854ad3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="8" r:id="Ra35d495b7eea4fad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Menu Mix" sheetId="9" r:id="Raa3e2e48059448c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Assumptions" sheetId="10" r:id="Re56058f3a9044313"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Forecast" sheetId="11" r:id="R67ce2fad23754824"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAPEX" sheetId="12" r:id="R2936b479061845de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPEX" sheetId="13" r:id="R5a9304e95bfa4097"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payroll" sheetId="14" r:id="Rff05f993f4cd42fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Food Cost" sheetId="15" r:id="R16e75298c1ab4dda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delivery Economics" sheetId="16" r:id="Rc086e8b7f17342b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="17" r:id="Rcd4dfb6809ca4e27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Break-Even" sheetId="18" r:id="R3b066e71371e407b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="19" r:id="R5c8691bb91374956"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario Analysis" sheetId="20" r:id="Rfa7cf2d4c28d4a58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="21" r:id="Rd0649dcec72f40e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="22" r:id="Re8313d72198d4af9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="23" r:id="Ra59de5a2497943cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Go No-Go Summary" sheetId="1" r:id="R0cd0b65faaf24a88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="Rd7f523dd4d494a56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Overview" sheetId="3" r:id="R6f5a90ee99ed4063"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Concept" sheetId="4" r:id="R7c6134d4565e439a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market Assumptions" sheetId="5" r:id="R12d5c7224a0b434c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Location" sheetId="6" r:id="Racf786195aea4536"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target Customer" sheetId="7" r:id="Rb20eb0593a0d45b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="8" r:id="R9c57139996af46ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Menu Mix" sheetId="9" r:id="Rc631509f97f74e96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Assumptions" sheetId="10" r:id="Rb5004161eaf44392"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Forecast" sheetId="11" r:id="Rcffb71d2994e43f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAPEX" sheetId="12" r:id="R191703230ff44f54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPEX" sheetId="13" r:id="R1ea62387c8e4471e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payroll" sheetId="14" r:id="R62bc442c506543fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Food Cost" sheetId="15" r:id="R631e9ae7fd9447a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delivery Economics" sheetId="16" r:id="R962807cd93c848f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="17" r:id="R7a8c34ad784d4870"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Break-Even" sheetId="18" r:id="R8cd0d896729a477c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="19" r:id="Ra010b147a04743a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario Analysis" sheetId="20" r:id="R51de97a87fe643e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="21" r:id="Rc8911569cf8a409c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="22" r:id="Rfc0717d445e0412c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="23" r:id="R3a76402796ec4823"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -157,6 +157,742 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="e1622446-9925-48aa-8eec-fcc584e40cfe"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R6aa93b1b051b4017"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="e9ff53cf-155f-4948-b74a-a146b24e5bc0"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R120bf596f9684264"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="940b2580-1944-4b6e-b978-06b0fab0baa2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R7a6964051f2c4472"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="4df82de4-6c6d-48a6-8472-5f2756296b36"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R982d6b7508514d6c"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="127869ef-b05a-4eab-9b31-c00ca70ff763"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R8d91ab7e87e5463a"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="8368d463-a6e7-477a-b2a4-2ac6c9fc6bb7"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R4a30bdfd01da4247"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="fda5f464-3ae3-49c2-8c79-27ade2c1d310"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra082f5f174a9461e"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="0c80e637-5798-40a3-a9b3-bf2c3ae69fe1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R7ae50911ba464e58"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="56796729-1321-42c9-8b01-c04f7bce7ec1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R5866a506babd45de"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="3f30f681-457a-4cc6-8211-302b4dd9cee0"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R50de6a72b5564598"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="8cbfe081-6b8f-4b67-aa76-a0702af831ed"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R1d316d9297514180"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="a82755fe-0328-4086-9c00-35365e2c9a56"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R24944021aadc4808"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="2ebb90a3-1dc6-4f3f-ab00-b9130b3fc245"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R29470a7a60714ca8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="fa31bebd-330b-403a-b06d-225c86cf949d"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R5c422e489685454a"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="b07e6531-5621-42cb-89a1-18c5b8a82c82"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R71a0698a67ea40b9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="e5555f97-98be-43b0-901c-7a878a56ad23"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R6939b523d1d54ca5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="ee1595fe-d9ca-479a-bf35-4bd9f8b8fcf8"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R58eeedbe68524449"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="3c4350c7-41ee-4c33-b2b9-55c04758a8ae"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R380b0ae6155342b0"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="a55ac2d9-3b7a-4946-a24d-eacf1f764a53"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R4e50bcf7ee8644d9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="b52b82cd-8a28-480c-a220-6c3f8dd45d5e"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra2ef3c0b415f470b"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="c12c8f4f-ac1e-40de-a542-a6a64fd21443"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rbcbe8d3e7bd24ecf"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="f5a08f75-7c5e-46f9-935d-537ea7839368"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R34db89f01a6f474c"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="455da9b7-44a4-4ff5-8499-ae2179189e8d"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra1f69c47ebc7489b"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -357,7 +1093,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -1441,6 +2177,7 @@
     <x:mergeCell ref="A14:H14"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73439e871a6d41d8"/>
 </x:worksheet>
 </file>
 
@@ -1451,7 +2188,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -2514,6 +3251,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8102d0eb2628442d"/>
 </x:worksheet>
 </file>
 
@@ -2540,7 +3278,7 @@
     <x:col min="14" max="14" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -3838,6 +4576,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2dd8e756c1f24130"/>
 </x:worksheet>
 </file>
 
@@ -3848,7 +4587,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -4990,6 +5729,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda42040ff76740ed"/>
 </x:worksheet>
 </file>
 
@@ -5000,7 +5740,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -6089,6 +6829,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref7ce9844fae48ed"/>
 </x:worksheet>
 </file>
 
@@ -6099,7 +6840,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -7233,6 +7974,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd36485b0d80643fc"/>
 </x:worksheet>
 </file>
 
@@ -7243,7 +7985,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -8306,6 +9048,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R270e61fefedb4301"/>
 </x:worksheet>
 </file>
 
@@ -8316,7 +9059,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -9379,6 +10122,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e30a95b801f47a5"/>
 </x:worksheet>
 </file>
 
@@ -9389,7 +10133,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -10775,6 +11519,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb023fad6374c4c71"/>
 </x:worksheet>
 </file>
 
@@ -10785,7 +11530,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -11856,6 +12601,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R107ba35d8ed64201"/>
 </x:worksheet>
 </file>
 
@@ -11866,7 +12612,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -13117,6 +13863,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R130445f428984dee"/>
 </x:worksheet>
 </file>
 
@@ -13133,7 +13880,7 @@
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -14269,6 +15016,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63a0a81179b64a20"/>
 </x:worksheet>
 </file>
 
@@ -14279,7 +15027,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -15342,6 +16090,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R303ddb8b04d347b2"/>
 </x:worksheet>
 </file>
 
@@ -15352,7 +16101,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -16415,6 +17164,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f6d3d6888be4c0e"/>
 </x:worksheet>
 </file>
 
@@ -16425,7 +17175,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -17544,6 +18294,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e6f0469d76445d8"/>
 </x:worksheet>
 </file>
 
@@ -17554,7 +18305,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -18617,6 +19368,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd72bff16cafd4e75"/>
 </x:worksheet>
 </file>
 
@@ -18627,7 +19379,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -19690,6 +20442,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6123c3e7d7774778"/>
 </x:worksheet>
 </file>
 
@@ -19700,7 +20453,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -20763,6 +21516,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e8c6854e3034963"/>
 </x:worksheet>
 </file>
 
@@ -20773,7 +21527,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -21836,6 +22590,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R239e869ab1774de8"/>
 </x:worksheet>
 </file>
 
@@ -21846,7 +22601,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -22909,6 +23664,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9dc338deac849dc"/>
 </x:worksheet>
 </file>
 
@@ -22919,7 +23675,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -23982,6 +24738,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f7b68b854944cc8"/>
 </x:worksheet>
 </file>
 
@@ -23992,7 +24749,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -25055,6 +25812,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf09c4ce89bc449af"/>
 </x:worksheet>
 </file>
 
@@ -25065,7 +25823,7 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -26128,5 +26886,6 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R179aa0e5233e48bb"/>
 </x:worksheet>
 </file>